--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigS4_distribution_construct_ablation_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigS4_distribution_construct_ablation_source_data.xlsx
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7932728647014362</v>
+        <v>0.8652368354749307</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7925485008818343</v>
+        <v>0.8701814058956916</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007243638196019475</v>
+        <v>-0.004944570420760908</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.009888815873015881</v>
+        <v>-0.01338601961252334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01211432387174971</v>
+        <v>0.003307920839414055</v>
       </c>
       <c r="I2" t="n">
         <v>126</v>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7354671682896974</v>
+        <v>0.8028879720630524</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7401227024191346</v>
+        <v>0.807294855346391</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0046555341294372</v>
+        <v>-0.004406883283338603</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.02014352457163186</v>
+        <v>-0.01326500767498723</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007405756463057225</v>
+        <v>0.004228251818167068</v>
       </c>
       <c r="I3" t="n">
         <v>126</v>
@@ -597,7 +597,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -618,19 +618,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7932728647014362</v>
+        <v>0.8652368354749307</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8222789115646258</v>
+        <v>0.8578357268833459</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.02900604686318964</v>
+        <v>0.007401108591584826</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.04338726065367482</v>
+        <v>-0.0009410456859814008</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.009099450753671528</v>
+        <v>0.01498131467627579</v>
       </c>
       <c r="I4" t="n">
         <v>126</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -671,19 +671,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7354671682896974</v>
+        <v>0.8028879720630524</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7685269300536295</v>
+        <v>0.8020353831550111</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.03305976176393211</v>
+        <v>0.0008525889080412963</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.04450890500041616</v>
+        <v>-0.01638521162950405</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01580330163232557</v>
+        <v>0.01578937515703856</v>
       </c>
       <c r="I5" t="n">
         <v>126</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5365016376921139</v>
+        <v>0.5643109095490048</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5458553791887125</v>
+        <v>0.5728143109095489</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009353741496598622</v>
+        <v>-0.008503401360544172</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.02425687741423761</v>
+        <v>-0.02086912164246504</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005300738543907021</v>
+        <v>0.002886680988184667</v>
       </c>
       <c r="I6" t="n">
         <v>126</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5344895218089964</v>
+        <v>0.5646070863979928</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5571326199141533</v>
+        <v>0.5681578760831241</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02264309810515686</v>
+        <v>-0.003550789685131228</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0489486185550975</v>
+        <v>-0.01433599772454021</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.004112169951507827</v>
+        <v>0.003366376536209357</v>
       </c>
       <c r="I7" t="n">
         <v>126</v>
@@ -809,7 +809,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.5365016376921139</v>
+        <v>0.5643109095490048</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5212899974804737</v>
+        <v>0.5331947593852355</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01521164021164023</v>
+        <v>0.03111615016376923</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.003813559322033882</v>
+        <v>0.02064788199532952</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03038722915636836</v>
+        <v>0.04243052240389331</v>
       </c>
       <c r="I8" t="n">
         <v>126</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5344895218089964</v>
+        <v>0.5646070863979928</v>
       </c>
       <c r="E9" t="n">
-        <v>0.524814032467275</v>
+        <v>0.5333112193788119</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009675489341721466</v>
+        <v>0.03129586701918097</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.003930731918453778</v>
+        <v>0.01766647747903979</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01972707033827111</v>
+        <v>0.04402033923042476</v>
       </c>
       <c r="I9" t="n">
         <v>126</v>
@@ -915,7 +915,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6121189216427312</v>
+        <v>0.5915217939027463</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6437389770723104</v>
+        <v>0.6322751322751322</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.03162005542957924</v>
+        <v>-0.04075333837238593</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0455966465178466</v>
+        <v>-0.05798591201186352</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.01566311011687342</v>
+        <v>-0.02616843033509701</v>
       </c>
       <c r="I10" t="n">
         <v>126</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5944430799871223</v>
+        <v>0.5847961674467321</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6215567422904922</v>
+        <v>0.6147018976577447</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.02711366230336987</v>
+        <v>-0.02990573021101262</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.04668202999497939</v>
+        <v>-0.04699521221270882</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.01353422833350656</v>
+        <v>-0.01654249738204114</v>
       </c>
       <c r="I11" t="n">
         <v>126</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.6121189216427312</v>
+        <v>0.5915217939027463</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4855127236079617</v>
+        <v>0.47713529856387</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1266061980347695</v>
+        <v>0.1143864953388763</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1076053968647524</v>
+        <v>0.09601206223230024</v>
       </c>
       <c r="H12" t="n">
-        <v>0.15010230147986</v>
+        <v>0.1411390077986669</v>
       </c>
       <c r="I12" t="n">
         <v>126</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1095,19 +1095,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.5944430799871223</v>
+        <v>0.5847961674467321</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4875094620692859</v>
+        <v>0.48469426754589</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1069336179178364</v>
+        <v>0.1001018999008422</v>
       </c>
       <c r="G13" t="n">
-        <v>0.08734802984135182</v>
+        <v>0.08444427776665293</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1309442046575186</v>
+        <v>0.1245690166529726</v>
       </c>
       <c r="I13" t="n">
         <v>126</v>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.7631960191484002</v>
+        <v>0.7131204333585286</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7446775006298816</v>
+        <v>0.702790375409423</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0185185185185186</v>
+        <v>0.01033005794910558</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01004016051540963</v>
+        <v>0.002989477040816313</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03024319336393431</v>
+        <v>0.0200023305618545</v>
       </c>
       <c r="I14" t="n">
         <v>126</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1201,19 +1201,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.648646437650146</v>
+        <v>0.6255483475910413</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6335836866599467</v>
+        <v>0.6184101906127056</v>
       </c>
       <c r="F15" t="n">
-        <v>0.01506275099019927</v>
+        <v>0.007138156978335641</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006229950137381006</v>
+        <v>-0.0008277644132017203</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02900409027641716</v>
+        <v>0.01446466058481921</v>
       </c>
       <c r="I15" t="n">
         <v>126</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1254,19 +1254,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7631960191484002</v>
+        <v>0.7131204333585286</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8024691358024691</v>
+        <v>0.7227576215671454</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.03927311665406896</v>
+        <v>-0.009637188208616809</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.05830076690293818</v>
+        <v>-0.02478741496598644</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02191661956604886</v>
+        <v>0.003376952632904961</v>
       </c>
       <c r="I16" t="n">
         <v>126</v>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.648646437650146</v>
+        <v>0.6255483475910413</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6894956488988536</v>
+        <v>0.6314740354144786</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.04084921124870766</v>
+        <v>-0.005925687823437276</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.06702166410954616</v>
+        <v>-0.02082921822257051</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02116650485713153</v>
+        <v>0.008043629443933255</v>
       </c>
       <c r="I17" t="n">
         <v>126</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>0.01449275362318841</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04547202797202796</v>
+        <v>0.06316985645933014</v>
       </c>
       <c r="I18" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J18" t="n">
         <v>11</v>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1410,17 +1410,17 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
-        <v>0.01449275362318841</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04617187499999999</v>
+        <v>0.06097560975609756</v>
       </c>
       <c r="I19" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J19" t="n">
         <v>11</v>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1459,17 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.08695652173913043</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.03331967213114754</v>
+        <v>0.01019897959183673</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1528044871794872</v>
+        <v>0.0625</v>
       </c>
       <c r="I20" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="J20" t="n">
         <v>11</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>D4CAL-V151-66fe1bb6b7d3</t>
+          <t>D4CAL-V16-e615cd349a49</t>
         </is>
       </c>
     </row>
